--- a/data.mn/public/datasets/livestock-by-type-en.xlsx
+++ b/data.mn/public/datasets/livestock-by-type-en.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,44 +413,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Camel</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cattle</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Goat</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Horse</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sheep</t>
         </is>
@@ -473,19 +461,19 @@
         <v>1970</v>
       </c>
       <c r="B2" t="n">
-        <v>633.5</v>
+        <v>633.51</v>
       </c>
       <c r="C2" t="n">
-        <v>2107.8</v>
+        <v>2107.83</v>
       </c>
       <c r="D2" t="n">
-        <v>4207</v>
+        <v>4206.98</v>
       </c>
       <c r="E2" t="n">
-        <v>2315</v>
+        <v>2315.02</v>
       </c>
       <c r="F2" t="n">
-        <v>13311.5</v>
+        <v>13311.46</v>
       </c>
     </row>
     <row r="3">
@@ -493,19 +481,19 @@
         <v>1971</v>
       </c>
       <c r="B3" t="n">
-        <v>632</v>
+        <v>632.01</v>
       </c>
       <c r="C3" t="n">
-        <v>2176.1</v>
+        <v>2176.12</v>
       </c>
       <c r="D3" t="n">
-        <v>4194.8</v>
+        <v>4194.78</v>
       </c>
       <c r="E3" t="n">
-        <v>2269.5</v>
+        <v>2269.52</v>
       </c>
       <c r="F3" t="n">
-        <v>13420.2</v>
+        <v>13420.17</v>
       </c>
     </row>
     <row r="4">
@@ -513,19 +501,19 @@
         <v>1972</v>
       </c>
       <c r="B4" t="n">
-        <v>625.1</v>
+        <v>625.0700000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2189.4</v>
+        <v>2189.38</v>
       </c>
       <c r="D4" t="n">
-        <v>4338.4</v>
+        <v>4338.41</v>
       </c>
       <c r="E4" t="n">
-        <v>2239.4</v>
+        <v>2239.39</v>
       </c>
       <c r="F4" t="n">
-        <v>13715.9</v>
+        <v>13715.85</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +521,19 @@
         <v>1973</v>
       </c>
       <c r="B5" t="n">
-        <v>602.9</v>
+        <v>602.87</v>
       </c>
       <c r="C5" t="n">
-        <v>2234.7</v>
+        <v>2234.74</v>
       </c>
       <c r="D5" t="n">
         <v>4442.2</v>
       </c>
       <c r="E5" t="n">
-        <v>2185.4</v>
+        <v>2185.36</v>
       </c>
       <c r="F5" t="n">
-        <v>14072.9</v>
+        <v>14072.91</v>
       </c>
     </row>
     <row r="6">
@@ -553,19 +541,19 @@
         <v>1974</v>
       </c>
       <c r="B6" t="n">
-        <v>606.6</v>
+        <v>606.5700000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>2364</v>
+        <v>2363.96</v>
       </c>
       <c r="D6" t="n">
-        <v>4574.4</v>
+        <v>4574.36</v>
       </c>
       <c r="E6" t="n">
-        <v>2264.9</v>
+        <v>2264.94</v>
       </c>
       <c r="F6" t="n">
-        <v>14503.7</v>
+        <v>14503.71</v>
       </c>
     </row>
     <row r="7">
@@ -576,16 +564,16 @@
         <v>617</v>
       </c>
       <c r="C7" t="n">
-        <v>2427.1</v>
+        <v>2427.08</v>
       </c>
       <c r="D7" t="n">
-        <v>4594.6</v>
+        <v>4594.58</v>
       </c>
       <c r="E7" t="n">
-        <v>2254.6</v>
+        <v>2254.62</v>
       </c>
       <c r="F7" t="n">
-        <v>14458.4</v>
+        <v>14458.35</v>
       </c>
     </row>
     <row r="8">
@@ -593,19 +581,19 @@
         <v>1976</v>
       </c>
       <c r="B8" t="n">
-        <v>607.3</v>
+        <v>607.27</v>
       </c>
       <c r="C8" t="n">
-        <v>2418.4</v>
+        <v>2418.43</v>
       </c>
       <c r="D8" t="n">
-        <v>4547.1</v>
+        <v>4547.08</v>
       </c>
       <c r="E8" t="n">
-        <v>2204.7</v>
+        <v>2204.66</v>
       </c>
       <c r="F8" t="n">
-        <v>13906.5</v>
+        <v>13906.49</v>
       </c>
     </row>
     <row r="9">
@@ -613,19 +601,19 @@
         <v>1977</v>
       </c>
       <c r="B9" t="n">
-        <v>609</v>
+        <v>608.97</v>
       </c>
       <c r="C9" t="n">
-        <v>2389.9</v>
+        <v>2389.86</v>
       </c>
       <c r="D9" t="n">
-        <v>4410.3</v>
+        <v>4410.31</v>
       </c>
       <c r="E9" t="n">
-        <v>2102.7</v>
+        <v>2102.71</v>
       </c>
       <c r="F9" t="n">
-        <v>13430.3</v>
+        <v>13430.29</v>
       </c>
     </row>
     <row r="10">
@@ -633,16 +621,16 @@
         <v>1978</v>
       </c>
       <c r="B10" t="n">
-        <v>608.6</v>
+        <v>608.5700000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>2481.2</v>
+        <v>2481.24</v>
       </c>
       <c r="D10" t="n">
-        <v>4704.7</v>
+        <v>4704.67</v>
       </c>
       <c r="E10" t="n">
-        <v>2078.5</v>
+        <v>2078.49</v>
       </c>
       <c r="F10" t="n">
         <v>14152.7</v>
@@ -653,19 +641,19 @@
         <v>1979</v>
       </c>
       <c r="B11" t="n">
-        <v>616.3</v>
+        <v>616.25</v>
       </c>
       <c r="C11" t="n">
-        <v>2454.3</v>
+        <v>2454.27</v>
       </c>
       <c r="D11" t="n">
         <v>4739.2</v>
       </c>
       <c r="E11" t="n">
-        <v>2079.9</v>
+        <v>2079.88</v>
       </c>
       <c r="F11" t="n">
-        <v>14372.5</v>
+        <v>14372.46</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +661,19 @@
         <v>1980</v>
       </c>
       <c r="B12" t="n">
-        <v>591.5</v>
+        <v>591.49</v>
       </c>
       <c r="C12" t="n">
         <v>2500.1</v>
       </c>
       <c r="D12" t="n">
-        <v>4566.8</v>
+        <v>4566.75</v>
       </c>
       <c r="E12" t="n">
-        <v>1985.4</v>
+        <v>1985.42</v>
       </c>
       <c r="F12" t="n">
-        <v>14230.7</v>
+        <v>14230.74</v>
       </c>
     </row>
     <row r="13">
@@ -693,19 +681,19 @@
         <v>1981</v>
       </c>
       <c r="B13" t="n">
-        <v>586.2</v>
+        <v>586.23</v>
       </c>
       <c r="C13" t="n">
-        <v>2376.3</v>
+        <v>2376.32</v>
       </c>
       <c r="D13" t="n">
-        <v>4595.4</v>
+        <v>4595.39</v>
       </c>
       <c r="E13" t="n">
-        <v>1991.2</v>
+        <v>1991.16</v>
       </c>
       <c r="F13" t="n">
-        <v>14714</v>
+        <v>14714.04</v>
       </c>
     </row>
     <row r="14">
@@ -713,19 +701,19 @@
         <v>1982</v>
       </c>
       <c r="B14" t="n">
-        <v>584.7</v>
+        <v>584.66</v>
       </c>
       <c r="C14" t="n">
-        <v>2395.5</v>
+        <v>2395.54</v>
       </c>
       <c r="D14" t="n">
-        <v>4801.8</v>
+        <v>4801.79</v>
       </c>
       <c r="E14" t="n">
-        <v>2027.9</v>
+        <v>2027.87</v>
       </c>
       <c r="F14" t="n">
-        <v>14954.8</v>
+        <v>14954.82</v>
       </c>
     </row>
     <row r="15">
@@ -733,19 +721,19 @@
         <v>1983</v>
       </c>
       <c r="B15" t="n">
-        <v>578</v>
+        <v>578.01</v>
       </c>
       <c r="C15" t="n">
-        <v>2373.9</v>
+        <v>2373.88</v>
       </c>
       <c r="D15" t="n">
-        <v>4548.5</v>
+        <v>4548.52</v>
       </c>
       <c r="E15" t="n">
-        <v>1959.6</v>
+        <v>1959.55</v>
       </c>
       <c r="F15" t="n">
-        <v>14110.4</v>
+        <v>14110.44</v>
       </c>
     </row>
     <row r="16">
@@ -753,19 +741,19 @@
         <v>1984</v>
       </c>
       <c r="B16" t="n">
-        <v>568.2</v>
+        <v>568.16</v>
       </c>
       <c r="C16" t="n">
-        <v>2373.9</v>
+        <v>2373.92</v>
       </c>
       <c r="D16" t="n">
         <v>4298</v>
       </c>
       <c r="E16" t="n">
-        <v>1960.9</v>
+        <v>1960.86</v>
       </c>
       <c r="F16" t="n">
-        <v>13391.2</v>
+        <v>13391.21</v>
       </c>
     </row>
     <row r="17">
@@ -773,19 +761,19 @@
         <v>1985</v>
       </c>
       <c r="B17" t="n">
-        <v>559</v>
+        <v>559.01</v>
       </c>
       <c r="C17" t="n">
-        <v>2408.1</v>
+        <v>2408.11</v>
       </c>
       <c r="D17" t="n">
         <v>4298.6</v>
       </c>
       <c r="E17" t="n">
-        <v>1971.1</v>
+        <v>1971.05</v>
       </c>
       <c r="F17" t="n">
-        <v>13248.8</v>
+        <v>13248.79</v>
       </c>
     </row>
     <row r="18">
@@ -793,19 +781,19 @@
         <v>1986</v>
       </c>
       <c r="B18" t="n">
-        <v>551</v>
+        <v>550.98</v>
       </c>
       <c r="C18" t="n">
-        <v>2468.5</v>
+        <v>2468.52</v>
       </c>
       <c r="D18" t="n">
-        <v>4384.4</v>
+        <v>4384.36</v>
       </c>
       <c r="E18" t="n">
-        <v>2017.6</v>
+        <v>2017.63</v>
       </c>
       <c r="F18" t="n">
-        <v>13169</v>
+        <v>13169.02</v>
       </c>
     </row>
     <row r="19">
@@ -813,19 +801,19 @@
         <v>1987</v>
       </c>
       <c r="B19" t="n">
-        <v>546.6</v>
+        <v>546.58</v>
       </c>
       <c r="C19" t="n">
-        <v>2526</v>
+        <v>2525.95</v>
       </c>
       <c r="D19" t="n">
-        <v>4387.7</v>
+        <v>4387.68</v>
       </c>
       <c r="E19" t="n">
-        <v>2047.2</v>
+        <v>2047.15</v>
       </c>
       <c r="F19" t="n">
-        <v>13233.8</v>
+        <v>13233.77</v>
       </c>
     </row>
     <row r="20">
@@ -833,19 +821,19 @@
         <v>1988</v>
       </c>
       <c r="B20" t="n">
-        <v>552.9</v>
+        <v>552.91</v>
       </c>
       <c r="C20" t="n">
-        <v>2541.3</v>
+        <v>2541.32</v>
       </c>
       <c r="D20" t="n">
-        <v>4474.3</v>
+        <v>4474.32</v>
       </c>
       <c r="E20" t="n">
-        <v>2103</v>
+        <v>2102.97</v>
       </c>
       <c r="F20" t="n">
-        <v>13450.8</v>
+        <v>13450.78</v>
       </c>
     </row>
     <row r="21">
@@ -853,19 +841,19 @@
         <v>1989</v>
       </c>
       <c r="B21" t="n">
-        <v>558.3</v>
+        <v>558.33</v>
       </c>
       <c r="C21" t="n">
-        <v>2692.7</v>
+        <v>2692.71</v>
       </c>
       <c r="D21" t="n">
-        <v>4959.2</v>
+        <v>4959.15</v>
       </c>
       <c r="E21" t="n">
-        <v>2199.6</v>
+        <v>2199.61</v>
       </c>
       <c r="F21" t="n">
-        <v>14265.2</v>
+        <v>14265.19</v>
       </c>
     </row>
     <row r="22">
@@ -876,16 +864,16 @@
         <v>537.5</v>
       </c>
       <c r="C22" t="n">
-        <v>2848.7</v>
+        <v>2848.71</v>
       </c>
       <c r="D22" t="n">
-        <v>5125.8</v>
+        <v>5125.75</v>
       </c>
       <c r="E22" t="n">
-        <v>2262.1</v>
+        <v>2262.05</v>
       </c>
       <c r="F22" t="n">
-        <v>15083</v>
+        <v>15082.96</v>
       </c>
     </row>
     <row r="23">
@@ -893,19 +881,19 @@
         <v>1991</v>
       </c>
       <c r="B23" t="n">
-        <v>476</v>
+        <v>476.02</v>
       </c>
       <c r="C23" t="n">
-        <v>2822</v>
+        <v>2822.04</v>
       </c>
       <c r="D23" t="n">
-        <v>5249.6</v>
+        <v>5249.59</v>
       </c>
       <c r="E23" t="n">
-        <v>2259.4</v>
+        <v>2259.35</v>
       </c>
       <c r="F23" t="n">
-        <v>14721</v>
+        <v>14720.98</v>
       </c>
     </row>
     <row r="24">
@@ -913,19 +901,19 @@
         <v>1992</v>
       </c>
       <c r="B24" t="n">
-        <v>415.2</v>
+        <v>415.17</v>
       </c>
       <c r="C24" t="n">
         <v>2819.2</v>
       </c>
       <c r="D24" t="n">
-        <v>5602.5</v>
+        <v>5602.53</v>
       </c>
       <c r="E24" t="n">
-        <v>2200.2</v>
+        <v>2200.18</v>
       </c>
       <c r="F24" t="n">
-        <v>14657</v>
+        <v>14657.01</v>
       </c>
     </row>
     <row r="25">
@@ -933,19 +921,19 @@
         <v>1993</v>
       </c>
       <c r="B25" t="n">
-        <v>363</v>
+        <v>363.03</v>
       </c>
       <c r="C25" t="n">
-        <v>2658.8</v>
+        <v>2658.75</v>
       </c>
       <c r="D25" t="n">
-        <v>6036.1</v>
+        <v>6036.14</v>
       </c>
       <c r="E25" t="n">
-        <v>2135.5</v>
+        <v>2135.46</v>
       </c>
       <c r="F25" t="n">
-        <v>13495</v>
+        <v>13494.97</v>
       </c>
     </row>
     <row r="26">
@@ -953,19 +941,19 @@
         <v>1994</v>
       </c>
       <c r="B26" t="n">
-        <v>366.1</v>
+        <v>366.14</v>
       </c>
       <c r="C26" t="n">
-        <v>2996.7</v>
+        <v>2996.68</v>
       </c>
       <c r="D26" t="n">
-        <v>7234.6</v>
+        <v>7234.63</v>
       </c>
       <c r="E26" t="n">
-        <v>2407.1</v>
+        <v>2407.06</v>
       </c>
       <c r="F26" t="n">
-        <v>13774</v>
+        <v>13773.99</v>
       </c>
     </row>
     <row r="27">
@@ -973,19 +961,19 @@
         <v>1995</v>
       </c>
       <c r="B27" t="n">
-        <v>367.5</v>
+        <v>367.51</v>
       </c>
       <c r="C27" t="n">
-        <v>3317.1</v>
+        <v>3317.05</v>
       </c>
       <c r="D27" t="n">
-        <v>8520.799999999999</v>
+        <v>8520.75</v>
       </c>
       <c r="E27" t="n">
-        <v>2648.4</v>
+        <v>2648.43</v>
       </c>
       <c r="F27" t="n">
-        <v>13718.6</v>
+        <v>13718.62</v>
       </c>
     </row>
     <row r="28">
@@ -993,16 +981,16 @@
         <v>1996</v>
       </c>
       <c r="B28" t="n">
-        <v>357.9</v>
+        <v>357.93</v>
       </c>
       <c r="C28" t="n">
-        <v>3476.3</v>
+        <v>3476.29</v>
       </c>
       <c r="D28" t="n">
-        <v>9134.9</v>
+        <v>9134.879999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>2770.5</v>
+        <v>2770.48</v>
       </c>
       <c r="F28" t="n">
         <v>13560.6</v>
@@ -1013,19 +1001,19 @@
         <v>1997</v>
       </c>
       <c r="B29" t="n">
-        <v>355.4</v>
+        <v>355.36</v>
       </c>
       <c r="C29" t="n">
-        <v>3612.9</v>
+        <v>3612.87</v>
       </c>
       <c r="D29" t="n">
-        <v>10265.3</v>
+        <v>10265.32</v>
       </c>
       <c r="E29" t="n">
-        <v>2893.2</v>
+        <v>2893.16</v>
       </c>
       <c r="F29" t="n">
-        <v>14165.6</v>
+        <v>14165.64</v>
       </c>
     </row>
     <row r="30">
@@ -1033,19 +1021,19 @@
         <v>1998</v>
       </c>
       <c r="B30" t="n">
-        <v>356.5</v>
+        <v>356.52</v>
       </c>
       <c r="C30" t="n">
-        <v>3725.8</v>
+        <v>3725.83</v>
       </c>
       <c r="D30" t="n">
-        <v>11061.9</v>
+        <v>11061.88</v>
       </c>
       <c r="E30" t="n">
-        <v>3059.1</v>
+        <v>3059.06</v>
       </c>
       <c r="F30" t="n">
-        <v>14694.3</v>
+        <v>14694.26</v>
       </c>
     </row>
     <row r="31">
@@ -1062,10 +1050,10 @@
         <v>11033.9</v>
       </c>
       <c r="E31" t="n">
-        <v>3163.5</v>
+        <v>3163.46</v>
       </c>
       <c r="F31" t="n">
-        <v>15191.3</v>
+        <v>15191.34</v>
       </c>
     </row>
     <row r="32">
@@ -1073,19 +1061,19 @@
         <v>2000</v>
       </c>
       <c r="B32" t="n">
-        <v>322.9</v>
+        <v>322.92</v>
       </c>
       <c r="C32" t="n">
-        <v>3097.6</v>
+        <v>3097.64</v>
       </c>
       <c r="D32" t="n">
-        <v>10269.8</v>
+        <v>10269.84</v>
       </c>
       <c r="E32" t="n">
-        <v>2660.7</v>
+        <v>2660.74</v>
       </c>
       <c r="F32" t="n">
-        <v>13876.4</v>
+        <v>13876.43</v>
       </c>
     </row>
     <row r="33">
@@ -1093,19 +1081,19 @@
         <v>2001</v>
       </c>
       <c r="B33" t="n">
-        <v>285.2</v>
+        <v>285.23</v>
       </c>
       <c r="C33" t="n">
-        <v>2069.6</v>
+        <v>2069.63</v>
       </c>
       <c r="D33" t="n">
-        <v>9591.299999999999</v>
+        <v>9591.34</v>
       </c>
       <c r="E33" t="n">
-        <v>2191.9</v>
+        <v>2191.87</v>
       </c>
       <c r="F33" t="n">
-        <v>11937.4</v>
+        <v>11937.35</v>
       </c>
     </row>
     <row r="34">
@@ -1113,19 +1101,19 @@
         <v>2002</v>
       </c>
       <c r="B34" t="n">
-        <v>253.1</v>
+        <v>253.07</v>
       </c>
       <c r="C34" t="n">
-        <v>1884.3</v>
+        <v>1884.28</v>
       </c>
       <c r="D34" t="n">
-        <v>9134.799999999999</v>
+        <v>9134.780000000001</v>
       </c>
       <c r="E34" t="n">
         <v>1988.9</v>
       </c>
       <c r="F34" t="n">
-        <v>10636.6</v>
+        <v>10636.62</v>
       </c>
     </row>
     <row r="35">
@@ -1133,19 +1121,19 @@
         <v>2003</v>
       </c>
       <c r="B35" t="n">
-        <v>256.7</v>
+        <v>256.74</v>
       </c>
       <c r="C35" t="n">
-        <v>1792.8</v>
+        <v>1792.77</v>
       </c>
       <c r="D35" t="n">
-        <v>10653</v>
+        <v>10652.97</v>
       </c>
       <c r="E35" t="n">
-        <v>1968.9</v>
+        <v>1968.91</v>
       </c>
       <c r="F35" t="n">
-        <v>10756.4</v>
+        <v>10756.41</v>
       </c>
     </row>
     <row r="36">
@@ -1153,19 +1141,19 @@
         <v>2004</v>
       </c>
       <c r="B36" t="n">
-        <v>256.6</v>
+        <v>256.61</v>
       </c>
       <c r="C36" t="n">
-        <v>1841.6</v>
+        <v>1841.61</v>
       </c>
       <c r="D36" t="n">
-        <v>12238</v>
+        <v>12238.04</v>
       </c>
       <c r="E36" t="n">
-        <v>2005.3</v>
+        <v>2005.28</v>
       </c>
       <c r="F36" t="n">
-        <v>11686.4</v>
+        <v>11686.43</v>
       </c>
     </row>
     <row r="37">
@@ -1173,19 +1161,19 @@
         <v>2005</v>
       </c>
       <c r="B37" t="n">
-        <v>254.2</v>
+        <v>254.19</v>
       </c>
       <c r="C37" t="n">
-        <v>1963.7</v>
+        <v>1963.65</v>
       </c>
       <c r="D37" t="n">
-        <v>13267.4</v>
+        <v>13267.39</v>
       </c>
       <c r="E37" t="n">
-        <v>2029.1</v>
+        <v>2029.09</v>
       </c>
       <c r="F37" t="n">
-        <v>12884.6</v>
+        <v>12884.55</v>
       </c>
     </row>
     <row r="38">
@@ -1193,19 +1181,19 @@
         <v>2006</v>
       </c>
       <c r="B38" t="n">
-        <v>253.3</v>
+        <v>253.27</v>
       </c>
       <c r="C38" t="n">
-        <v>2167.9</v>
+        <v>2167.91</v>
       </c>
       <c r="D38" t="n">
         <v>15451.7</v>
       </c>
       <c r="E38" t="n">
-        <v>2114.8</v>
+        <v>2114.77</v>
       </c>
       <c r="F38" t="n">
-        <v>14815.1</v>
+        <v>14815.09</v>
       </c>
     </row>
     <row r="39">
@@ -1216,16 +1204,16 @@
         <v>260.6</v>
       </c>
       <c r="C39" t="n">
-        <v>2425.8</v>
+        <v>2425.82</v>
       </c>
       <c r="D39" t="n">
-        <v>18347.9</v>
+        <v>18347.85</v>
       </c>
       <c r="E39" t="n">
         <v>2239.5</v>
       </c>
       <c r="F39" t="n">
-        <v>16990.1</v>
+        <v>16990.11</v>
       </c>
     </row>
     <row r="40">
@@ -1233,7 +1221,7 @@
         <v>2008</v>
       </c>
       <c r="B40" t="n">
-        <v>266.4</v>
+        <v>266.43</v>
       </c>
       <c r="C40" t="n">
         <v>2503.4</v>
@@ -1242,10 +1230,10 @@
         <v>19969.4</v>
       </c>
       <c r="E40" t="n">
-        <v>2187</v>
+        <v>2186.95</v>
       </c>
       <c r="F40" t="n">
-        <v>18362.4</v>
+        <v>18362.37</v>
       </c>
     </row>
     <row r="41">
@@ -1253,19 +1241,19 @@
         <v>2009</v>
       </c>
       <c r="B41" t="n">
-        <v>277.1</v>
+        <v>277.05</v>
       </c>
       <c r="C41" t="n">
-        <v>2599.4</v>
+        <v>2599.35</v>
       </c>
       <c r="D41" t="n">
-        <v>19651.5</v>
+        <v>19651.54</v>
       </c>
       <c r="E41" t="n">
-        <v>2221.3</v>
+        <v>2221.33</v>
       </c>
       <c r="F41" t="n">
-        <v>19274.8</v>
+        <v>19274.75</v>
       </c>
     </row>
     <row r="42">
@@ -1273,16 +1261,16 @@
         <v>2010</v>
       </c>
       <c r="B42" t="n">
-        <v>269.6</v>
+        <v>269.61</v>
       </c>
       <c r="C42" t="n">
         <v>2176</v>
       </c>
       <c r="D42" t="n">
-        <v>13883.2</v>
+        <v>13883.24</v>
       </c>
       <c r="E42" t="n">
-        <v>1920.3</v>
+        <v>1920.34</v>
       </c>
       <c r="F42" t="n">
         <v>14480.4</v>
@@ -1293,19 +1281,19 @@
         <v>2011</v>
       </c>
       <c r="B43" t="n">
-        <v>280.1</v>
+        <v>280.09</v>
       </c>
       <c r="C43" t="n">
-        <v>2339.7</v>
+        <v>2339.71</v>
       </c>
       <c r="D43" t="n">
-        <v>15934.6</v>
+        <v>15934.58</v>
       </c>
       <c r="E43" t="n">
-        <v>2112.9</v>
+        <v>2112.94</v>
       </c>
       <c r="F43" t="n">
-        <v>15668.5</v>
+        <v>15668.54</v>
       </c>
     </row>
     <row r="44">
@@ -1313,19 +1301,19 @@
         <v>2012</v>
       </c>
       <c r="B44" t="n">
-        <v>305.8</v>
+        <v>305.83</v>
       </c>
       <c r="C44" t="n">
-        <v>2584.6</v>
+        <v>2584.62</v>
       </c>
       <c r="D44" t="n">
-        <v>17558.7</v>
+        <v>17558.67</v>
       </c>
       <c r="E44" t="n">
-        <v>2330.4</v>
+        <v>2330.43</v>
       </c>
       <c r="F44" t="n">
-        <v>18141.4</v>
+        <v>18141.36</v>
       </c>
     </row>
     <row r="45">
@@ -1333,19 +1321,19 @@
         <v>2013</v>
       </c>
       <c r="B45" t="n">
-        <v>321.5</v>
+        <v>321.48</v>
       </c>
       <c r="C45" t="n">
-        <v>2909.5</v>
+        <v>2909.46</v>
       </c>
       <c r="D45" t="n">
-        <v>19227.6</v>
+        <v>19227.58</v>
       </c>
       <c r="E45" t="n">
-        <v>2619.4</v>
+        <v>2619.38</v>
       </c>
       <c r="F45" t="n">
-        <v>20066.4</v>
+        <v>20066.43</v>
       </c>
     </row>
     <row r="46">
@@ -1356,16 +1344,16 @@
         <v>349.3</v>
       </c>
       <c r="C46" t="n">
-        <v>3413.9</v>
+        <v>3413.85</v>
       </c>
       <c r="D46" t="n">
         <v>22008.9</v>
       </c>
       <c r="E46" t="n">
-        <v>2995.8</v>
+        <v>2995.75</v>
       </c>
       <c r="F46" t="n">
-        <v>23214.8</v>
+        <v>23214.78</v>
       </c>
     </row>
     <row r="47">
@@ -1373,19 +1361,19 @@
         <v>2015</v>
       </c>
       <c r="B47" t="n">
-        <v>368</v>
+        <v>367.99</v>
       </c>
       <c r="C47" t="n">
         <v>3780.4</v>
       </c>
       <c r="D47" t="n">
-        <v>23592.9</v>
+        <v>23592.92</v>
       </c>
       <c r="E47" t="n">
-        <v>3295.3</v>
+        <v>3295.34</v>
       </c>
       <c r="F47" t="n">
-        <v>24943.1</v>
+        <v>24943.13</v>
       </c>
     </row>
     <row r="48">
@@ -1393,16 +1381,16 @@
         <v>2016</v>
       </c>
       <c r="B48" t="n">
-        <v>401.3</v>
+        <v>401.35</v>
       </c>
       <c r="C48" t="n">
-        <v>4080.9</v>
+        <v>4080.94</v>
       </c>
       <c r="D48" t="n">
-        <v>25574.9</v>
+        <v>25574.86</v>
       </c>
       <c r="E48" t="n">
-        <v>3635.5</v>
+        <v>3635.49</v>
       </c>
       <c r="F48" t="n">
         <v>27856.6</v>
@@ -1416,16 +1404,16 @@
         <v>434.1</v>
       </c>
       <c r="C49" t="n">
-        <v>4388.5</v>
+        <v>4388.46</v>
       </c>
       <c r="D49" t="n">
-        <v>27346.7</v>
+        <v>27346.71</v>
       </c>
       <c r="E49" t="n">
-        <v>3939.8</v>
+        <v>3939.81</v>
       </c>
       <c r="F49" t="n">
-        <v>30109.9</v>
+        <v>30109.89</v>
       </c>
     </row>
     <row r="50">
@@ -1436,13 +1424,13 @@
         <v>459.7</v>
       </c>
       <c r="C50" t="n">
-        <v>4380.9</v>
+        <v>4380.88</v>
       </c>
       <c r="D50" t="n">
         <v>27124.7</v>
       </c>
       <c r="E50" t="n">
-        <v>3940.1</v>
+        <v>3940.09</v>
       </c>
       <c r="F50" t="n">
         <v>30554.8</v>
@@ -1453,19 +1441,19 @@
         <v>2019</v>
       </c>
       <c r="B51" t="n">
-        <v>472.4</v>
+        <v>472.38</v>
       </c>
       <c r="C51" t="n">
-        <v>4753.2</v>
+        <v>4753.19</v>
       </c>
       <c r="D51" t="n">
-        <v>29261.7</v>
+        <v>29261.66</v>
       </c>
       <c r="E51" t="n">
-        <v>4214.8</v>
+        <v>4214.82</v>
       </c>
       <c r="F51" t="n">
-        <v>32267.3</v>
+        <v>32267.27</v>
       </c>
     </row>
     <row r="52">
@@ -1473,19 +1461,19 @@
         <v>2020</v>
       </c>
       <c r="B52" t="n">
-        <v>472.9</v>
+        <v>472.93</v>
       </c>
       <c r="C52" t="n">
-        <v>4732</v>
+        <v>4732.01</v>
       </c>
       <c r="D52" t="n">
-        <v>27720.3</v>
+        <v>27720.25</v>
       </c>
       <c r="E52" t="n">
-        <v>4093.9</v>
+        <v>4093.86</v>
       </c>
       <c r="F52" t="n">
-        <v>30049.4</v>
+        <v>30049.43</v>
       </c>
     </row>
     <row r="53">
@@ -1493,19 +1481,19 @@
         <v>2021</v>
       </c>
       <c r="B53" t="n">
-        <v>454</v>
+        <v>454.04</v>
       </c>
       <c r="C53" t="n">
-        <v>5022.2</v>
+        <v>5022.23</v>
       </c>
       <c r="D53" t="n">
-        <v>26456.1</v>
+        <v>26456.09</v>
       </c>
       <c r="E53" t="n">
-        <v>4324.4</v>
+        <v>4324.44</v>
       </c>
       <c r="F53" t="n">
-        <v>31087</v>
+        <v>31086.96</v>
       </c>
     </row>
     <row r="54">
@@ -1513,19 +1501,19 @@
         <v>2022</v>
       </c>
       <c r="B54" t="n">
-        <v>470.5</v>
+        <v>470.47</v>
       </c>
       <c r="C54" t="n">
-        <v>5512.8</v>
+        <v>5512.84</v>
       </c>
       <c r="D54" t="n">
         <v>27569.4</v>
       </c>
       <c r="E54" t="n">
-        <v>4821.1</v>
+        <v>4821.07</v>
       </c>
       <c r="F54" t="n">
-        <v>32747.7</v>
+        <v>32747.68</v>
       </c>
     </row>
     <row r="55">
@@ -1533,19 +1521,19 @@
         <v>2023</v>
       </c>
       <c r="B55" t="n">
-        <v>473.9</v>
+        <v>473.85</v>
       </c>
       <c r="C55" t="n">
-        <v>5350.8</v>
+        <v>5350.76</v>
       </c>
       <c r="D55" t="n">
-        <v>24618.2</v>
+        <v>24618.23</v>
       </c>
       <c r="E55" t="n">
-        <v>4829.7</v>
+        <v>4829.69</v>
       </c>
       <c r="F55" t="n">
-        <v>29409.4</v>
+        <v>29409.35</v>
       </c>
     </row>
     <row r="56">
@@ -1553,19 +1541,39 @@
         <v>2024</v>
       </c>
       <c r="B56" t="n">
-        <v>480.6</v>
+        <v>480.57</v>
       </c>
       <c r="C56" t="n">
-        <v>5074.6</v>
+        <v>5074.55</v>
       </c>
       <c r="D56" t="n">
-        <v>22920.2</v>
+        <v>22920.18</v>
       </c>
       <c r="E56" t="n">
-        <v>4683.2</v>
+        <v>4683.23</v>
       </c>
       <c r="F56" t="n">
-        <v>24491.1</v>
+        <v>24491.12</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B57" t="n">
+        <v>501.26</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5441.51</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23170.31</v>
+      </c>
+      <c r="E57" t="n">
+        <v>5128.67</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23862.46</v>
       </c>
     </row>
   </sheetData>
